--- a/docs/research/legacy/旧站素材迁移报告.xlsx
+++ b/docs/research/legacy/旧站素材迁移报告.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johns\Downloads\ai-website-cloner-template-master\docs\research\legacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3321AD8C-E4E9-4F91-84D4-13EC9D39B0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2194" yWindow="2194" windowWidth="24686" windowHeight="13595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15317"/>
   </bookViews>
   <sheets>
     <sheet name="①需重新提供的图片" sheetId="1" r:id="rId1"/>
@@ -36,12 +35,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="107">
   <si>
     <t>需要甲方重新提供的产品图片</t>
   </si>
   <si>
-    <t>旧站 2022 年上传的这批图，产品主体上压着对角线域名水印，无法去除，因此未采用。请甲方提供无水印原图。</t>
+    <t>旧站 2022 年上传的这批图，产品主体上压着对角线域名水印，无法去除，因此未采用。请提供无水印原图。</t>
   </si>
   <si>
     <t>型号</t>
@@ -159,9 +158,6 @@
   </si>
   <si>
     <t>合计</t>
-  </si>
-  <si>
-    <t>说明：这三个型号的规格文字已经采用，只有图片需要重新提供。若甲方能给出无水印原图，直接放进 CMS 后台的「图库」字段即可，不需要改代码。</t>
   </si>
   <si>
     <t>材质 / 表面处理 / 适用门型 —— 两个来源对不上</t>
@@ -365,54 +361,218 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="9"/>
       <color rgb="FF0563C1"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Microsoft YaHei"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -422,25 +582,215 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -463,9 +813,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -477,34 +1069,78 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -789,14 +1425,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -807,7 +1443,7 @@
     <col min="7" max="7" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="20.149999999999999">
+    <row r="1" ht="20.1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -817,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
+    <row r="4" ht="30" customHeight="1" spans="1:7">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -840,283 +1476,283 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="25.75">
-      <c r="A5" s="4" t="s">
+    <row r="5" ht="25.7" spans="1:7">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25.75">
-      <c r="A6" s="4" t="s">
+    <row r="6" ht="25.7" spans="1:7">
+      <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="25.75">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="25.7" spans="1:7">
+      <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="25.75">
-      <c r="A8" s="4" t="s">
+    <row r="8" ht="25.7" spans="1:7">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.75">
-      <c r="A9" s="4" t="s">
+    <row r="9" ht="25.7" spans="1:7">
+      <c r="A9" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="25.75">
-      <c r="A10" s="4" t="s">
+    <row r="10" ht="25.7" spans="1:7">
+      <c r="A10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="25.75">
-      <c r="A11" s="4" t="s">
+    <row r="11" ht="25.7" spans="1:7">
+      <c r="A11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="25.75">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="25.7" spans="1:7">
+      <c r="A12" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.75">
-      <c r="A13" s="4" t="s">
+    <row r="13" ht="25.7" spans="1:7">
+      <c r="A13" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.45">
-      <c r="A14" s="4" t="s">
+    <row r="14" ht="27.45" spans="1:7">
+      <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="27.45">
-      <c r="A15" s="4" t="s">
+    <row r="15" ht="27.45" spans="1:7">
+      <c r="A15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.45">
-      <c r="A16" s="4" t="s">
+    <row r="16" ht="27.45" spans="1:7">
+      <c r="A16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15">
+    <row r="18" ht="14.55" spans="1:3">
       <c r="A18" s="7" t="s">
         <v>40</v>
       </c>
@@ -1126,45 +1762,45 @@
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="A20" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="G5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G6" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="F7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="G7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="F8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="G8" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="F9" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="G9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="F10" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="G10" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="F11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="G11" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F12" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="G12" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F13" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="G13" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="F14" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="G14" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F15" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="G15" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F16" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="G16" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="F5" r:id="rId1" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615144M38.gif"/>
+    <hyperlink ref="G5" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F6" r:id="rId3" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615144I24.jpg"/>
+    <hyperlink ref="G6" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F7" r:id="rId4" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615144RT.jpg"/>
+    <hyperlink ref="G7" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F8" r:id="rId5" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615144c35.jpg"/>
+    <hyperlink ref="G8" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F9" r:id="rId6" display="https://www.cantonlock.com/uploads/allimg/20220926/2-220926151449615.jpg"/>
+    <hyperlink ref="G9" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F10" r:id="rId7" display="https://www.cantonlock.com/uploads/allimg/20220926/2-220926151450424.jpg"/>
+    <hyperlink ref="G10" r:id="rId2" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=387&amp;lang=en"/>
+    <hyperlink ref="F11" r:id="rId8" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615255E27.jpg"/>
+    <hyperlink ref="G11" r:id="rId9" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=391&amp;lang=en"/>
+    <hyperlink ref="F12" r:id="rId10" display="https://www.cantonlock.com/uploads/allimg/20220926/2-220926152556292.jpg"/>
+    <hyperlink ref="G12" r:id="rId9" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=391&amp;lang=en"/>
+    <hyperlink ref="F13" r:id="rId11" display="https://www.cantonlock.com/uploads/allimg/20220926/2-22092615255S11.jpg"/>
+    <hyperlink ref="G13" r:id="rId9" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=391&amp;lang=en"/>
+    <hyperlink ref="F14" r:id="rId12" display="https://www.cantonlock.com/uploads/allimg/20220927/2-22092GH00IZ.jpg"/>
+    <hyperlink ref="G14" r:id="rId13" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=506&amp;lang=en"/>
+    <hyperlink ref="F15" r:id="rId14" display="https://www.cantonlock.com/uploads/allimg/20220927/2-22092GH00K36.jpg"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=506&amp;lang=en"/>
+    <hyperlink ref="F16" r:id="rId15" display="https://www.cantonlock.com/uploads/allimg/20220927/2-22092GH00R18.jpg"/>
+    <hyperlink ref="G16" r:id="rId13" display="https://www.cantonlock.com/index.php?m=home&amp;c=View&amp;a=index&amp;aid=506&amp;lang=en"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1174,270 +1810,272 @@
     <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.149999999999999">
+    <row r="1" ht="20.1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="5" ht="27.45" spans="1:6">
+      <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="27.45">
-      <c r="A5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="8" t="s">
+      <c r="C6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="C8" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="C9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="8" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="8" t="s">
+      <c r="C11" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C12" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1446,81 +2084,83 @@
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="20.149999999999999">
+    <row r="1" ht="20.1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="5" ht="27.45" spans="1:5">
+      <c r="A5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="41.15">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="4" t="s">
+    </row>
+    <row r="6" ht="41.15" spans="1:5">
+      <c r="A6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="41.15">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1529,17 +2169,17 @@
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20.149999999999999">
+    <row r="1" ht="20.1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1547,141 +2187,141 @@
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="4">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="10">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10">
-        <v>2</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="10" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="4">
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="10">
+      <c r="F6" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4">
         <v>5</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D7" s="4">
         <v>8</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="10" t="s">
+      <c r="E7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C7" s="10">
-        <v>5</v>
-      </c>
-      <c r="D7" s="10">
-        <v>8</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="8">
+      <c r="E8" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="5">
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D9" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="9" t="s">
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" ht="14.55" spans="1:6">
+      <c r="A12" s="7" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="8">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="8">
-        <v>0</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15">
-      <c r="A12" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="C12" s="7">
         <f>SUM(C5:C10)</f>
@@ -1690,10 +2330,11 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>